--- a/Result/profitability/6161.xlsx
+++ b/Result/profitability/6161.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.64125</v>
+        <v>0.7675</v>
       </c>
       <c r="N2" t="n">
-        <v>32.59125</v>
+        <v>31.4375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.52</v>
+        <v>0.6675</v>
       </c>
       <c r="N3" t="n">
-        <v>27.4325</v>
+        <v>26.7225</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0.41625</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>22.71875</v>
+        <v>22.25375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.17625</v>
+        <v>0.31875</v>
       </c>
       <c r="N5" t="n">
-        <v>17.515</v>
+        <v>17.315</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1925</v>
+        <v>0.30625</v>
       </c>
       <c r="N6" t="n">
-        <v>13.955</v>
+        <v>14.55875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.10375</v>
+        <v>0.225</v>
       </c>
       <c r="N7" t="n">
-        <v>10.93125</v>
+        <v>11.63</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05624999999999999</v>
+        <v>0.1675</v>
       </c>
       <c r="N8" t="n">
-        <v>7.999999999999999</v>
+        <v>7.87375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.44</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0075</v>
+        <v>0.007499999999999972</v>
       </c>
       <c r="N9" t="n">
         <v>4.355</v>
@@ -1645,7 +1645,7 @@
         <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02</v>
+        <v>0.01999999999999997</v>
       </c>
       <c r="N10" t="n">
         <v>4.4025</v>
@@ -1772,7 +1772,7 @@
         <v>0.29</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08875</v>
+        <v>0.08874999999999997</v>
       </c>
       <c r="N11" t="n">
         <v>4.8625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6161</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>451</v>
+      </c>
+      <c r="D75" t="n">
+        <v>293</v>
+      </c>
+      <c r="E75" t="n">
+        <v>158</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>70</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>46</v>
+      </c>
+      <c r="J75" t="n">
+        <v>116</v>
+      </c>
+      <c r="K75" t="n">
+        <v>97</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.81375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.3225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.072289156626506</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.009999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02807115063924392</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.96551724137931</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0437517090511349</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
